--- a/xlsx/secttable.xlsx
+++ b/xlsx/secttable.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,6 +409,12 @@
       <c r="C1" t="str">
         <v>description</v>
       </c>
+      <c r="D1" t="str">
+        <v>backColor</v>
+      </c>
+      <c r="E1" t="str">
+        <v>emblemColor</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -420,6 +426,12 @@
       <c r="C2" t="str">
         <v>소속 종파가 없음.</v>
       </c>
+      <c r="D2" t="str">
+        <v>#3a3a55</v>
+      </c>
+      <c r="E2" t="str">
+        <v>#5a5a8a</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -431,10 +443,16 @@
       <c r="C3" t="str">
         <v>검을 수련하는 종파.</v>
       </c>
+      <c r="D3" t="str">
+        <v>#1f4a3a</v>
+      </c>
+      <c r="E3" t="str">
+        <v>#3a8866</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>